--- a/KNK업무시스템구축/01_HAIST_WORKS/_전직원_로그인계정_2026-04-28.xlsx
+++ b/KNK업무시스템구축/01_HAIST_WORKS/_전직원_로그인계정_2026-04-28.xlsx
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>(미등록)</t>
+          <t>lyh</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2930,7 +2930,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>▣ DB 미등록 인원(이름 일치 안 됨): 1명 → 이용호</t>
+          <t>▣ DB 미등록 인원(이름 일치 안 됨): 0명 → 없음</t>
         </is>
       </c>
     </row>
